--- a/gu_in/Item.edf/38_UnitUpper/UnitUpper.xlsx
+++ b/gu_in/Item.edf/38_UnitUpper/UnitUpper.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5653D742-0858-4CB5-B124-46363FBF5889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA55B64-4F62-4018-8F3C-9B890DC7F0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitUpper" sheetId="1" r:id="rId1"/>
@@ -823,7 +823,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -832,8 +832,15 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -848,6 +855,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -881,17 +893,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -908,9 +923,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -948,9 +963,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -983,9 +998,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1018,9 +1050,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1195,60 +1244,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BB82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="34" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="9" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="40" max="41" width="7" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="9" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="9" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="9" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="9" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1412,7 +1461,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1574,7 +1623,7 @@
       </c>
       <c r="BB2" s="2"/>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>57</v>
       </c>
@@ -1737,7 +1786,7 @@
       </c>
       <c r="BB3" s="2"/>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>60</v>
       </c>
@@ -1900,7 +1949,7 @@
       </c>
       <c r="BB4" s="2"/>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -2063,7 +2112,7 @@
       </c>
       <c r="BB5" s="2"/>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -2226,7 +2275,7 @@
       </c>
       <c r="BB6" s="2"/>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>63</v>
       </c>
@@ -2389,7 +2438,7 @@
       </c>
       <c r="BB7" s="2"/>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>64</v>
       </c>
@@ -2552,7 +2601,7 @@
       </c>
       <c r="BB8" s="2"/>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>65</v>
       </c>
@@ -2715,7 +2764,7 @@
       </c>
       <c r="BB9" s="2"/>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
@@ -2878,7 +2927,7 @@
       </c>
       <c r="BB10" s="2"/>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>68</v>
       </c>
@@ -3041,7 +3090,7 @@
       </c>
       <c r="BB11" s="2"/>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
@@ -3204,7 +3253,7 @@
       </c>
       <c r="BB12" s="2"/>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>72</v>
       </c>
@@ -3367,7 +3416,7 @@
       </c>
       <c r="BB13" s="2"/>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>74</v>
       </c>
@@ -3530,7 +3579,7 @@
       </c>
       <c r="BB14" s="2"/>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>255</v>
       </c>
@@ -3564,8 +3613,8 @@
       <c r="K15" s="2">
         <v>0</v>
       </c>
-      <c r="L15" s="3">
-        <v>50</v>
+      <c r="L15" s="5">
+        <v>51</v>
       </c>
       <c r="M15" s="3">
         <v>-1</v>
@@ -3693,7 +3742,7 @@
       </c>
       <c r="BB15" s="2"/>
     </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>76</v>
       </c>
@@ -3727,8 +3776,8 @@
       <c r="K16" s="2">
         <v>0</v>
       </c>
-      <c r="L16" s="3">
-        <v>50</v>
+      <c r="L16" s="5">
+        <v>51</v>
       </c>
       <c r="M16" s="3">
         <v>-1</v>
@@ -3856,7 +3905,7 @@
       </c>
       <c r="BB16" s="2"/>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>77</v>
       </c>
@@ -3890,8 +3939,8 @@
       <c r="K17" s="2">
         <v>0</v>
       </c>
-      <c r="L17" s="3">
-        <v>50</v>
+      <c r="L17" s="5">
+        <v>51</v>
       </c>
       <c r="M17" s="3">
         <v>-1</v>
@@ -4019,7 +4068,7 @@
       </c>
       <c r="BB17" s="2"/>
     </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>78</v>
       </c>
@@ -4182,7 +4231,7 @@
       </c>
       <c r="BB18" s="2"/>
     </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>80</v>
       </c>
@@ -4345,7 +4394,7 @@
       </c>
       <c r="BB19" s="2"/>
     </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>81</v>
       </c>
@@ -4508,7 +4557,7 @@
       </c>
       <c r="BB20" s="2"/>
     </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>82</v>
       </c>
@@ -4671,7 +4720,7 @@
       </c>
       <c r="BB21" s="2"/>
     </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>84</v>
       </c>
@@ -4834,7 +4883,7 @@
       </c>
       <c r="BB22" s="2"/>
     </row>
-    <row r="23" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>85</v>
       </c>
@@ -4997,7 +5046,7 @@
       </c>
       <c r="BB23" s="2"/>
     </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>88</v>
       </c>
@@ -5160,7 +5209,7 @@
       </c>
       <c r="BB24" s="2"/>
     </row>
-    <row r="25" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>89</v>
       </c>
@@ -5323,7 +5372,7 @@
       </c>
       <c r="BB25" s="2"/>
     </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>90</v>
       </c>
@@ -5486,7 +5535,7 @@
       </c>
       <c r="BB26" s="2"/>
     </row>
-    <row r="27" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>92</v>
       </c>
@@ -5649,7 +5698,7 @@
       </c>
       <c r="BB27" s="2"/>
     </row>
-    <row r="28" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>93</v>
       </c>
@@ -5812,7 +5861,7 @@
       </c>
       <c r="BB28" s="2"/>
     </row>
-    <row r="29" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>94</v>
       </c>
@@ -5975,7 +6024,7 @@
       </c>
       <c r="BB29" s="2"/>
     </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>95</v>
       </c>
@@ -6138,7 +6187,7 @@
       </c>
       <c r="BB30" s="2"/>
     </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>97</v>
       </c>
@@ -6301,7 +6350,7 @@
       </c>
       <c r="BB31" s="2"/>
     </row>
-    <row r="32" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>99</v>
       </c>
@@ -6464,7 +6513,7 @@
       </c>
       <c r="BB32" s="2"/>
     </row>
-    <row r="33" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>101</v>
       </c>
@@ -6627,7 +6676,7 @@
       </c>
       <c r="BB33" s="2"/>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>103</v>
       </c>
@@ -6790,7 +6839,7 @@
       </c>
       <c r="BB34" s="2"/>
     </row>
-    <row r="35" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>104</v>
       </c>
@@ -6824,8 +6873,8 @@
       <c r="K35" s="2">
         <v>0</v>
       </c>
-      <c r="L35" s="3">
-        <v>50</v>
+      <c r="L35" s="5">
+        <v>51</v>
       </c>
       <c r="M35" s="3">
         <v>-1</v>
@@ -6953,7 +7002,7 @@
       </c>
       <c r="BB35" s="2"/>
     </row>
-    <row r="36" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>106</v>
       </c>
@@ -6987,8 +7036,8 @@
       <c r="K36" s="2">
         <v>0</v>
       </c>
-      <c r="L36" s="3">
-        <v>50</v>
+      <c r="L36" s="5">
+        <v>51</v>
       </c>
       <c r="M36" s="3">
         <v>-1</v>
@@ -7116,7 +7165,7 @@
       </c>
       <c r="BB36" s="2"/>
     </row>
-    <row r="37" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>107</v>
       </c>
@@ -7150,8 +7199,8 @@
       <c r="K37" s="2">
         <v>0</v>
       </c>
-      <c r="L37" s="3">
-        <v>50</v>
+      <c r="L37" s="5">
+        <v>51</v>
       </c>
       <c r="M37" s="3">
         <v>-1</v>
@@ -7279,7 +7328,7 @@
       </c>
       <c r="BB37" s="2"/>
     </row>
-    <row r="38" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>108</v>
       </c>
@@ -7442,7 +7491,7 @@
       </c>
       <c r="BB38" s="2"/>
     </row>
-    <row r="39" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>110</v>
       </c>
@@ -7605,7 +7654,7 @@
       </c>
       <c r="BB39" s="2"/>
     </row>
-    <row r="40" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>111</v>
       </c>
@@ -7768,7 +7817,7 @@
       </c>
       <c r="BB40" s="2"/>
     </row>
-    <row r="41" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>112</v>
       </c>
@@ -7931,7 +7980,7 @@
       </c>
       <c r="BB41" s="2"/>
     </row>
-    <row r="42" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>114</v>
       </c>
@@ -8094,7 +8143,7 @@
       </c>
       <c r="BB42" s="2"/>
     </row>
-    <row r="43" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>115</v>
       </c>
@@ -8257,7 +8306,7 @@
       </c>
       <c r="BB43" s="2"/>
     </row>
-    <row r="44" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>118</v>
       </c>
@@ -8420,7 +8469,7 @@
       </c>
       <c r="BB44" s="2"/>
     </row>
-    <row r="45" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>120</v>
       </c>
@@ -8583,7 +8632,7 @@
       </c>
       <c r="BB45" s="2"/>
     </row>
-    <row r="46" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>122</v>
       </c>
@@ -8746,7 +8795,7 @@
       </c>
       <c r="BB46" s="2"/>
     </row>
-    <row r="47" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>124</v>
       </c>
@@ -8909,7 +8958,7 @@
       </c>
       <c r="BB47" s="2"/>
     </row>
-    <row r="48" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>126</v>
       </c>
@@ -9072,7 +9121,7 @@
       </c>
       <c r="BB48" s="2"/>
     </row>
-    <row r="49" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>128</v>
       </c>
@@ -9235,7 +9284,7 @@
       </c>
       <c r="BB49" s="2"/>
     </row>
-    <row r="50" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>130</v>
       </c>
@@ -9398,7 +9447,7 @@
       </c>
       <c r="BB50" s="2"/>
     </row>
-    <row r="51" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>132</v>
       </c>
@@ -9561,7 +9610,7 @@
       </c>
       <c r="BB51" s="2"/>
     </row>
-    <row r="52" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>134</v>
       </c>
@@ -9724,7 +9773,7 @@
       </c>
       <c r="BB52" s="2"/>
     </row>
-    <row r="53" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>136</v>
       </c>
@@ -9887,7 +9936,7 @@
       </c>
       <c r="BB53" s="2"/>
     </row>
-    <row r="54" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>138</v>
       </c>
@@ -10050,7 +10099,7 @@
       </c>
       <c r="BB54" s="2"/>
     </row>
-    <row r="55" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>140</v>
       </c>
@@ -10213,7 +10262,7 @@
       </c>
       <c r="BB55" s="2"/>
     </row>
-    <row r="56" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>142</v>
       </c>
@@ -10376,7 +10425,7 @@
       </c>
       <c r="BB56" s="2"/>
     </row>
-    <row r="57" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>144</v>
       </c>
@@ -10539,7 +10588,7 @@
       </c>
       <c r="BB57" s="2"/>
     </row>
-    <row r="58" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>146</v>
       </c>
@@ -10702,7 +10751,7 @@
       </c>
       <c r="BB58" s="2"/>
     </row>
-    <row r="59" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>148</v>
       </c>
@@ -10865,7 +10914,7 @@
       </c>
       <c r="BB59" s="2"/>
     </row>
-    <row r="60" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>150</v>
       </c>
@@ -11028,7 +11077,7 @@
       </c>
       <c r="BB60" s="2"/>
     </row>
-    <row r="61" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>152</v>
       </c>
@@ -11191,7 +11240,7 @@
       </c>
       <c r="BB61" s="2"/>
     </row>
-    <row r="62" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>154</v>
       </c>
@@ -11354,7 +11403,7 @@
       </c>
       <c r="BB62" s="2"/>
     </row>
-    <row r="63" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>156</v>
       </c>
@@ -11517,7 +11566,7 @@
       </c>
       <c r="BB63" s="2"/>
     </row>
-    <row r="64" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>159</v>
       </c>
@@ -11680,7 +11729,7 @@
       </c>
       <c r="BB64" s="2"/>
     </row>
-    <row r="65" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>161</v>
       </c>
@@ -11843,7 +11892,7 @@
       </c>
       <c r="BB65" s="2"/>
     </row>
-    <row r="66" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>163</v>
       </c>
@@ -12006,7 +12055,7 @@
       </c>
       <c r="BB66" s="2"/>
     </row>
-    <row r="67" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>165</v>
       </c>
@@ -12169,7 +12218,7 @@
       </c>
       <c r="BB67" s="2"/>
     </row>
-    <row r="68" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>167</v>
       </c>
@@ -12332,7 +12381,7 @@
       </c>
       <c r="BB68" s="2"/>
     </row>
-    <row r="69" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>169</v>
       </c>
@@ -12495,7 +12544,7 @@
       </c>
       <c r="BB69" s="2"/>
     </row>
-    <row r="70" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>171</v>
       </c>
@@ -12658,7 +12707,7 @@
       </c>
       <c r="BB70" s="2"/>
     </row>
-    <row r="71" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>173</v>
       </c>
@@ -12821,7 +12870,7 @@
       </c>
       <c r="BB71" s="2"/>
     </row>
-    <row r="72" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>175</v>
       </c>
@@ -12984,7 +13033,7 @@
       </c>
       <c r="BB72" s="2"/>
     </row>
-    <row r="73" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>177</v>
       </c>
@@ -13147,7 +13196,7 @@
       </c>
       <c r="BB73" s="2"/>
     </row>
-    <row r="74" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>179</v>
       </c>
@@ -13310,7 +13359,7 @@
       </c>
       <c r="BB74" s="2"/>
     </row>
-    <row r="75" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>181</v>
       </c>
@@ -13473,7 +13522,7 @@
       </c>
       <c r="BB75" s="2"/>
     </row>
-    <row r="76" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>183</v>
       </c>
@@ -13636,7 +13685,7 @@
       </c>
       <c r="BB76" s="2"/>
     </row>
-    <row r="77" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>185</v>
       </c>
@@ -13799,7 +13848,7 @@
       </c>
       <c r="BB77" s="2"/>
     </row>
-    <row r="78" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>187</v>
       </c>
@@ -13962,7 +14011,7 @@
       </c>
       <c r="BB78" s="2"/>
     </row>
-    <row r="79" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>189</v>
       </c>
@@ -14125,7 +14174,7 @@
       </c>
       <c r="BB79" s="2"/>
     </row>
-    <row r="80" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>191</v>
       </c>
@@ -14288,7 +14337,7 @@
       </c>
       <c r="BB80" s="2"/>
     </row>
-    <row r="81" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>193</v>
       </c>
@@ -14451,7 +14500,7 @@
       </c>
       <c r="BB81" s="2"/>
     </row>
-    <row r="82" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>195</v>
       </c>
@@ -14623,53 +14672,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AZ82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="6" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="44" max="45" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>197</v>
       </c>
@@ -14827,7 +14876,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>UnitUpper!A2</f>
         <v>Code</v>
@@ -15007,7 +15056,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>UnitUpper!A3</f>
         <v>unup001</v>
@@ -15187,7 +15236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>UnitUpper!A4</f>
         <v>unup002</v>
@@ -15367,7 +15416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>UnitUpper!A5</f>
         <v>unup003</v>
@@ -15547,7 +15596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>UnitUpper!A6</f>
         <v>unup004</v>
@@ -15727,7 +15776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>UnitUpper!A7</f>
         <v>unup005</v>
@@ -15907,7 +15956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>UnitUpper!A8</f>
         <v>unup006</v>
@@ -16087,7 +16136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>UnitUpper!A9</f>
         <v>unup007</v>
@@ -16267,7 +16316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>UnitUpper!A10</f>
         <v>unup008</v>
@@ -16447,7 +16496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>UnitUpper!A11</f>
         <v>unup009</v>
@@ -16627,7 +16676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>UnitUpper!A12</f>
         <v>unup010</v>
@@ -16807,7 +16856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>UnitUpper!A13</f>
         <v>unup011</v>
@@ -16987,7 +17036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>UnitUpper!A14</f>
         <v>unup012</v>
@@ -17167,7 +17216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>UnitUpper!A15</f>
         <v>if5pt00</v>
@@ -17307,7 +17356,7 @@
       </c>
       <c r="AO15">
         <f>UnitUpper!L15</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP15">
         <f>UnitUpper!N15</f>
@@ -17347,7 +17396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>UnitUpper!A16</f>
         <v>unup014</v>
@@ -17487,7 +17536,7 @@
       </c>
       <c r="AO16">
         <f>UnitUpper!L16</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP16">
         <f>UnitUpper!N16</f>
@@ -17527,7 +17576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>UnitUpper!A17</f>
         <v>unup015</v>
@@ -17667,7 +17716,7 @@
       </c>
       <c r="AO17">
         <f>UnitUpper!L17</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP17">
         <f>UnitUpper!N17</f>
@@ -17707,7 +17756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>UnitUpper!A18</f>
         <v>unup016</v>
@@ -17887,7 +17936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>UnitUpper!A19</f>
         <v>unup017</v>
@@ -18067,7 +18116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>UnitUpper!A20</f>
         <v>unup018</v>
@@ -18247,7 +18296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>UnitUpper!A21</f>
         <v>unup019</v>
@@ -18427,7 +18476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>UnitUpper!A22</f>
         <v>unup020</v>
@@ -18607,7 +18656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>UnitUpper!A23</f>
         <v>unup021</v>
@@ -18787,7 +18836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>UnitUpper!A24</f>
         <v>unup022</v>
@@ -18967,7 +19016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>UnitUpper!A25</f>
         <v>unup023</v>
@@ -19147,7 +19196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>UnitUpper!A26</f>
         <v>unup024</v>
@@ -19327,7 +19376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>UnitUpper!A27</f>
         <v>unup025</v>
@@ -19507,7 +19556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>UnitUpper!A28</f>
         <v>unup026</v>
@@ -19687,7 +19736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>UnitUpper!A29</f>
         <v>unup027</v>
@@ -19867,7 +19916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>UnitUpper!A30</f>
         <v>unup028</v>
@@ -20047,7 +20096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>UnitUpper!A31</f>
         <v>unup029</v>
@@ -20227,7 +20276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>UnitUpper!A32</f>
         <v>unup030</v>
@@ -20407,7 +20456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>UnitUpper!A33</f>
         <v>unup031</v>
@@ -20587,7 +20636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>UnitUpper!A34</f>
         <v>unup032</v>
@@ -20767,7 +20816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f>UnitUpper!A35</f>
         <v>unup033</v>
@@ -20907,7 +20956,7 @@
       </c>
       <c r="AO35">
         <f>UnitUpper!L35</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP35">
         <f>UnitUpper!N35</f>
@@ -20947,7 +20996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f>UnitUpper!A36</f>
         <v>unup034</v>
@@ -21087,7 +21136,7 @@
       </c>
       <c r="AO36">
         <f>UnitUpper!L36</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP36">
         <f>UnitUpper!N36</f>
@@ -21127,7 +21176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f>UnitUpper!A37</f>
         <v>unup035</v>
@@ -21267,7 +21316,7 @@
       </c>
       <c r="AO37">
         <f>UnitUpper!L37</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP37">
         <f>UnitUpper!N37</f>
@@ -21307,7 +21356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f>UnitUpper!A38</f>
         <v>unup036</v>
@@ -21487,7 +21536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f>UnitUpper!A39</f>
         <v>unup037</v>
@@ -21667,7 +21716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f>UnitUpper!A40</f>
         <v>unup038</v>
@@ -21847,7 +21896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f>UnitUpper!A41</f>
         <v>unup039</v>
@@ -22027,7 +22076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f>UnitUpper!A42</f>
         <v>unup040</v>
@@ -22207,7 +22256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f>UnitUpper!A43</f>
         <v>unup041</v>
@@ -22387,7 +22436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f>UnitUpper!A44</f>
         <v>unup042</v>
@@ -22567,7 +22616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>UnitUpper!A45</f>
         <v>unup043</v>
@@ -22747,7 +22796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f>UnitUpper!A46</f>
         <v>unup044</v>
@@ -22927,7 +22976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f>UnitUpper!A47</f>
         <v>unup045</v>
@@ -23107,7 +23156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f>UnitUpper!A48</f>
         <v>unup046</v>
@@ -23287,7 +23336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f>UnitUpper!A49</f>
         <v>unup047</v>
@@ -23467,7 +23516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f>UnitUpper!A50</f>
         <v>unup048</v>
@@ -23647,7 +23696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f>UnitUpper!A51</f>
         <v>unup049</v>
@@ -23827,7 +23876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f>UnitUpper!A52</f>
         <v>unup050</v>
@@ -24007,7 +24056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f>UnitUpper!A53</f>
         <v>unup051</v>
@@ -24187,7 +24236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f>UnitUpper!A54</f>
         <v>unup052</v>
@@ -24367,7 +24416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f>UnitUpper!A55</f>
         <v>unup053</v>
@@ -24547,7 +24596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f>UnitUpper!A56</f>
         <v>unup054</v>
@@ -24727,7 +24776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f>UnitUpper!A57</f>
         <v>unup055</v>
@@ -24907,7 +24956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f>UnitUpper!A58</f>
         <v>unup056</v>
@@ -25087,7 +25136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
         <f>UnitUpper!A59</f>
         <v>unup057</v>
@@ -25267,7 +25316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f>UnitUpper!A60</f>
         <v>unup058</v>
@@ -25447,7 +25496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
         <f>UnitUpper!A61</f>
         <v>unup059</v>
@@ -25627,7 +25676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
         <f>UnitUpper!A62</f>
         <v>unup060</v>
@@ -25807,7 +25856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
         <f>UnitUpper!A63</f>
         <v>unup061</v>
@@ -25987,7 +26036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f>UnitUpper!A64</f>
         <v>unup062</v>
@@ -26167,7 +26216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
         <f>UnitUpper!A65</f>
         <v>unup063</v>
@@ -26347,7 +26396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
         <f>UnitUpper!A66</f>
         <v>unup064</v>
@@ -26527,7 +26576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
         <f>UnitUpper!A67</f>
         <v>unup065</v>
@@ -26707,7 +26756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <f>UnitUpper!A68</f>
         <v>unup066</v>
@@ -26887,7 +26936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
         <f>UnitUpper!A69</f>
         <v>unup067</v>
@@ -27067,7 +27116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
         <f>UnitUpper!A70</f>
         <v>unup068</v>
@@ -27247,7 +27296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
         <f>UnitUpper!A71</f>
         <v>unup069</v>
@@ -27427,7 +27476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
         <f>UnitUpper!A72</f>
         <v>unup070</v>
@@ -27607,7 +27656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
         <f>UnitUpper!A73</f>
         <v>unup071</v>
@@ -27787,7 +27836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
         <f>UnitUpper!A74</f>
         <v>unup072</v>
@@ -27967,7 +28016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
         <f>UnitUpper!A75</f>
         <v>unup073</v>
@@ -28147,7 +28196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
         <f>UnitUpper!A76</f>
         <v>unup074</v>
@@ -28327,7 +28376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
         <f>UnitUpper!A77</f>
         <v>unup075</v>
@@ -28507,7 +28556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
         <f>UnitUpper!A78</f>
         <v>unup076</v>
@@ -28687,7 +28736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
         <f>UnitUpper!A79</f>
         <v>unup077</v>
@@ -28867,7 +28916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
         <f>UnitUpper!A80</f>
         <v>unup078</v>
@@ -29047,7 +29096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
         <f>UnitUpper!A81</f>
         <v>unup079</v>
@@ -29227,7 +29276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
         <f>UnitUpper!A82</f>
         <v>unup080</v>
@@ -29416,9 +29465,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -29429,7 +29478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>202</v>
       </c>
@@ -29438,7 +29487,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>0</v>
       </c>
@@ -29447,7 +29496,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -29456,7 +29505,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -29465,7 +29514,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -29474,7 +29523,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -29483,7 +29532,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -29492,7 +29541,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -29501,7 +29550,7 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -29510,7 +29559,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -29519,7 +29568,7 @@
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -29528,7 +29577,7 @@
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -29537,7 +29586,7 @@
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>11</v>
       </c>
@@ -29546,7 +29595,7 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -29555,7 +29604,7 @@
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -29564,7 +29613,7 @@
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -29573,7 +29622,7 @@
       </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>15</v>
       </c>
@@ -29582,7 +29631,7 @@
       </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -29591,7 +29640,7 @@
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -29600,7 +29649,7 @@
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>18</v>
       </c>
@@ -29609,7 +29658,7 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>19</v>
       </c>
@@ -29618,7 +29667,7 @@
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>20</v>
       </c>
@@ -29627,7 +29676,7 @@
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>21</v>
       </c>
@@ -29636,7 +29685,7 @@
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>22</v>
       </c>
@@ -29645,7 +29694,7 @@
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>23</v>
       </c>
@@ -29654,7 +29703,7 @@
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>24</v>
       </c>
@@ -29663,7 +29712,7 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>25</v>
       </c>
@@ -29672,7 +29721,7 @@
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>26</v>
       </c>
@@ -29681,7 +29730,7 @@
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>27</v>
       </c>
@@ -29690,7 +29739,7 @@
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>28</v>
       </c>
@@ -29699,7 +29748,7 @@
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>29</v>
       </c>
@@ -29708,7 +29757,7 @@
       </c>
       <c r="C32" s="2"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>30</v>
       </c>
@@ -29717,7 +29766,7 @@
       </c>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>31</v>
       </c>
@@ -29726,7 +29775,7 @@
       </c>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>32</v>
       </c>
@@ -29735,7 +29784,7 @@
       </c>
       <c r="C35" s="2"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>33</v>
       </c>
@@ -29744,7 +29793,7 @@
       </c>
       <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>34</v>
       </c>
@@ -29753,7 +29802,7 @@
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>35</v>
       </c>
@@ -29762,7 +29811,7 @@
       </c>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>36</v>
       </c>
@@ -29771,7 +29820,7 @@
       </c>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>37</v>
       </c>
@@ -29780,7 +29829,7 @@
       </c>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>38</v>
       </c>
@@ -29789,7 +29838,7 @@
       </c>
       <c r="C41" s="2"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>39</v>
       </c>
@@ -29798,7 +29847,7 @@
       </c>
       <c r="C42" s="2"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>40</v>
       </c>
@@ -29807,7 +29856,7 @@
       </c>
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>41</v>
       </c>
@@ -29816,7 +29865,7 @@
       </c>
       <c r="C44" s="2"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>42</v>
       </c>
@@ -29825,7 +29874,7 @@
       </c>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>43</v>
       </c>
@@ -29834,7 +29883,7 @@
       </c>
       <c r="C46" s="2"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>44</v>
       </c>
@@ -29843,7 +29892,7 @@
       </c>
       <c r="C47" s="2"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>45</v>
       </c>
@@ -29852,7 +29901,7 @@
       </c>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>46</v>
       </c>
@@ -29861,7 +29910,7 @@
       </c>
       <c r="C49" s="2"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>47</v>
       </c>
@@ -29870,7 +29919,7 @@
       </c>
       <c r="C50" s="2"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>48</v>
       </c>
@@ -29879,7 +29928,7 @@
       </c>
       <c r="C51" s="2"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>49</v>
       </c>
@@ -29888,7 +29937,7 @@
       </c>
       <c r="C52" s="2"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>50</v>
       </c>
@@ -29897,7 +29946,7 @@
       </c>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>51</v>
       </c>
@@ -29906,7 +29955,7 @@
       </c>
       <c r="C54" s="2"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>52</v>
       </c>
@@ -29915,7 +29964,7 @@
       </c>
       <c r="C55" s="2"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>53</v>
       </c>
@@ -29924,7 +29973,7 @@
       </c>
       <c r="C56" s="2"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>54</v>
       </c>
@@ -29933,7 +29982,7 @@
       </c>
       <c r="C57" s="2"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>55</v>
       </c>
@@ -29942,7 +29991,7 @@
       </c>
       <c r="C58" s="2"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>56</v>
       </c>
@@ -29951,7 +30000,7 @@
       </c>
       <c r="C59" s="2"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>57</v>
       </c>
@@ -29960,7 +30009,7 @@
       </c>
       <c r="C60" s="2"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>58</v>
       </c>
@@ -29969,7 +30018,7 @@
       </c>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>59</v>
       </c>
@@ -29978,7 +30027,7 @@
       </c>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>60</v>
       </c>
@@ -29987,7 +30036,7 @@
       </c>
       <c r="C63" s="2"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>61</v>
       </c>
@@ -29996,7 +30045,7 @@
       </c>
       <c r="C64" s="2"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>62</v>
       </c>
@@ -30005,7 +30054,7 @@
       </c>
       <c r="C65" s="2"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>63</v>
       </c>
@@ -30014,7 +30063,7 @@
       </c>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>64</v>
       </c>
@@ -30023,7 +30072,7 @@
       </c>
       <c r="C67" s="2"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>65</v>
       </c>
@@ -30032,7 +30081,7 @@
       </c>
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>66</v>
       </c>
@@ -30041,7 +30090,7 @@
       </c>
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>67</v>
       </c>
@@ -30050,7 +30099,7 @@
       </c>
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>68</v>
       </c>
@@ -30059,7 +30108,7 @@
       </c>
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>69</v>
       </c>
@@ -30068,7 +30117,7 @@
       </c>
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>70</v>
       </c>
@@ -30077,7 +30126,7 @@
       </c>
       <c r="C73" s="2"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>71</v>
       </c>
@@ -30086,7 +30135,7 @@
       </c>
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>72</v>
       </c>
@@ -30095,7 +30144,7 @@
       </c>
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>73</v>
       </c>
@@ -30104,7 +30153,7 @@
       </c>
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>74</v>
       </c>
@@ -30113,7 +30162,7 @@
       </c>
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>75</v>
       </c>
@@ -30122,7 +30171,7 @@
       </c>
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>76</v>
       </c>
@@ -30131,7 +30180,7 @@
       </c>
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>77</v>
       </c>
@@ -30140,7 +30189,7 @@
       </c>
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>78</v>
       </c>
@@ -30149,7 +30198,7 @@
       </c>
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>79</v>
       </c>

--- a/gu_in/Item.edf/38_UnitUpper/UnitUpper.xlsx
+++ b/gu_in/Item.edf/38_UnitUpper/UnitUpper.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA55B64-4F62-4018-8F3C-9B890DC7F0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ABD1F5A-7DAA-4B57-822E-72A8A5138D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -823,7 +823,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -839,8 +839,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -860,6 +867,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -893,20 +905,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -6676,168 +6693,168 @@
       </c>
       <c r="BB33" s="2"/>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:54" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" s="3">
+      <c r="B34" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="6">
         <v>5</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="E34" s="3">
-        <v>1</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="E34" s="6">
+        <v>1</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="I34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J34" s="2">
-        <v>0</v>
-      </c>
-      <c r="K34" s="2">
-        <v>0</v>
-      </c>
-      <c r="L34" s="3">
+      <c r="G34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="I34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="J34" s="7">
+        <v>0</v>
+      </c>
+      <c r="K34" s="7">
+        <v>0</v>
+      </c>
+      <c r="L34" s="6">
         <v>48</v>
       </c>
-      <c r="M34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="N34" s="3">
-        <v>2</v>
-      </c>
-      <c r="O34" s="3">
+      <c r="M34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="N34" s="6">
+        <v>2</v>
+      </c>
+      <c r="O34" s="6">
         <v>95</v>
       </c>
-      <c r="P34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="Q34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="R34" s="2">
-        <v>1</v>
-      </c>
-      <c r="S34" s="2">
-        <v>0</v>
-      </c>
-      <c r="T34" s="2">
-        <v>0</v>
-      </c>
-      <c r="U34" s="2">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2">
-        <v>0</v>
-      </c>
-      <c r="W34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="X34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y34" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="2">
+      <c r="P34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R34" s="7">
+        <v>1</v>
+      </c>
+      <c r="S34" s="7">
+        <v>0</v>
+      </c>
+      <c r="T34" s="7">
+        <v>0</v>
+      </c>
+      <c r="U34" s="7">
+        <v>0</v>
+      </c>
+      <c r="V34" s="7">
+        <v>0</v>
+      </c>
+      <c r="W34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="X34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="7">
         <v>50</v>
       </c>
-      <c r="AA34" s="2">
+      <c r="AA34" s="7">
         <v>50</v>
       </c>
-      <c r="AB34" s="3">
-        <v>2891</v>
-      </c>
-      <c r="AC34" s="3">
+      <c r="AB34" s="6">
+        <v>2591</v>
+      </c>
+      <c r="AC34" s="6">
         <v>49</v>
       </c>
-      <c r="AD34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AE34" s="3">
+      <c r="AD34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="AE34" s="6">
         <v>13</v>
       </c>
-      <c r="AF34" s="3">
+      <c r="AF34" s="6">
         <v>13</v>
       </c>
-      <c r="AG34" s="3">
+      <c r="AG34" s="6">
         <v>13</v>
       </c>
-      <c r="AH34" s="3">
+      <c r="AH34" s="6">
         <v>13</v>
       </c>
-      <c r="AI34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="3">
+      <c r="AI34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="6">
         <v>1900000</v>
       </c>
-      <c r="AK34" s="3">
-        <v>1</v>
-      </c>
-      <c r="AL34" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM34" s="2">
+      <c r="AK34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM34" s="7">
         <v>38000</v>
       </c>
-      <c r="AN34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY34" s="2" t="str">
+      <c r="AN34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AW34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AX34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AY34" s="7" t="str">
         <f t="shared" si="0"/>
         <v>tunup032</v>
       </c>
-      <c r="AZ34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="BA34" s="3">
-        <v>2</v>
-      </c>
-      <c r="BB34" s="2"/>
+      <c r="AZ34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BA34" s="6">
+        <v>2</v>
+      </c>
+      <c r="BB34" s="7"/>
     </row>
     <row r="35" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
@@ -20730,7 +20747,7 @@
       </c>
       <c r="AB34">
         <f>UnitUpper!AB34</f>
-        <v>2891</v>
+        <v>2591</v>
       </c>
       <c r="AC34">
         <f>UnitUpper!AE34</f>

--- a/gu_in/Item.edf/38_UnitUpper/UnitUpper.xlsx
+++ b/gu_in/Item.edf/38_UnitUpper/UnitUpper.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ABD1F5A-7DAA-4B57-822E-72A8A5138D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B01A8A-9CFE-43AE-82C6-FB38B35B953B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6800,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="6">
-        <v>1900000</v>
+        <v>90909382</v>
       </c>
       <c r="AK34" s="6">
         <v>1</v>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="I34">
         <f>UnitUpper!AJ34</f>
-        <v>1900000</v>
+        <v>90909382</v>
       </c>
       <c r="J34">
         <f>UnitUpper!AK34</f>

--- a/gu_in/Item.edf/38_UnitUpper/UnitUpper.xlsx
+++ b/gu_in/Item.edf/38_UnitUpper/UnitUpper.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B01A8A-9CFE-43AE-82C6-FB38B35B953B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED01DE3-A94E-47AC-B363-477D003E11D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitUpper" sheetId="1" r:id="rId1"/>
@@ -847,7 +847,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -872,6 +872,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -910,7 +916,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -920,6 +926,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -940,9 +949,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -980,9 +989,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1015,26 +1024,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1067,26 +1059,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3433,168 +3408,168 @@
       </c>
       <c r="BB13" s="2"/>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:54" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="3">
-        <v>2</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="C14" s="9">
+        <v>2</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="9">
+        <v>1</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H14" s="2">
-        <v>-1</v>
-      </c>
-      <c r="I14" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="G14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="10">
+        <v>0</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
         <v>48</v>
       </c>
-      <c r="M14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="N14" s="3">
-        <v>2</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="M14" s="9">
+        <v>-1</v>
+      </c>
+      <c r="N14" s="9">
+        <v>2</v>
+      </c>
+      <c r="O14" s="9">
         <v>95</v>
       </c>
-      <c r="P14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="R14" s="2">
-        <v>1</v>
-      </c>
-      <c r="S14" s="2">
-        <v>0</v>
-      </c>
-      <c r="T14" s="2">
-        <v>0</v>
-      </c>
-      <c r="U14" s="2">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2">
-        <v>0</v>
-      </c>
-      <c r="W14" s="2">
-        <v>-1</v>
-      </c>
-      <c r="X14" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="2">
+      <c r="P14" s="9">
+        <v>-1</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R14" s="10">
+        <v>1</v>
+      </c>
+      <c r="S14" s="10">
+        <v>0</v>
+      </c>
+      <c r="T14" s="10">
+        <v>0</v>
+      </c>
+      <c r="U14" s="10">
+        <v>0</v>
+      </c>
+      <c r="V14" s="10">
+        <v>0</v>
+      </c>
+      <c r="W14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="X14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="Y14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="10">
         <v>50</v>
       </c>
-      <c r="AA14" s="2">
+      <c r="AA14" s="10">
         <v>50</v>
       </c>
-      <c r="AB14" s="3">
-        <v>4996</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AB14" s="9">
+        <v>4596</v>
+      </c>
+      <c r="AC14" s="9">
         <v>49</v>
       </c>
-      <c r="AD14" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AD14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="AE14" s="9">
         <v>23</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="9">
         <v>23</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="9">
         <v>23</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="9">
         <v>23</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="3">
-        <v>1900000</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>1</v>
-      </c>
-      <c r="AL14" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM14" s="2">
-        <v>38000</v>
-      </c>
-      <c r="AN14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY14" s="2" t="str">
+      <c r="AI14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="6">
+        <v>3727272</v>
+      </c>
+      <c r="AK14" s="9">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="9">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="6">
+        <v>372727</v>
+      </c>
+      <c r="AN14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tunup012</v>
       </c>
-      <c r="AZ14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="BA14" s="3">
-        <v>2</v>
-      </c>
-      <c r="BB14" s="2"/>
+      <c r="AZ14" s="9">
+        <v>-1</v>
+      </c>
+      <c r="BA14" s="9">
+        <v>2</v>
+      </c>
+      <c r="BB14" s="10"/>
     </row>
     <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
@@ -6800,7 +6775,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="6">
-        <v>90909382</v>
+        <v>3727272</v>
       </c>
       <c r="AK34" s="6">
         <v>1</v>
@@ -6808,8 +6783,8 @@
       <c r="AL34" s="6">
         <v>1</v>
       </c>
-      <c r="AM34" s="7">
-        <v>38000</v>
+      <c r="AM34" s="6">
+        <v>372727</v>
       </c>
       <c r="AN34" s="7">
         <v>0</v>
@@ -17085,7 +17060,7 @@
       </c>
       <c r="I14">
         <f>UnitUpper!AJ14</f>
-        <v>1900000</v>
+        <v>3727272</v>
       </c>
       <c r="J14">
         <f>UnitUpper!AK14</f>
@@ -17147,7 +17122,7 @@
       </c>
       <c r="AB14">
         <f>UnitUpper!AB14</f>
-        <v>4996</v>
+        <v>4596</v>
       </c>
       <c r="AC14">
         <f>UnitUpper!AE14</f>
@@ -20685,7 +20660,7 @@
       </c>
       <c r="I34">
         <f>UnitUpper!AJ34</f>
-        <v>90909382</v>
+        <v>3727272</v>
       </c>
       <c r="J34">
         <f>UnitUpper!AK34</f>

--- a/gu_in/Item.edf/38_UnitUpper/UnitUpper.xlsx
+++ b/gu_in/Item.edf/38_UnitUpper/UnitUpper.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED01DE3-A94E-47AC-B363-477D003E11D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A29CB8-4EF7-441D-B724-8083A3E7FEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitUpper" sheetId="1" r:id="rId1"/>
@@ -949,9 +949,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -989,9 +989,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1024,9 +1024,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1059,9 +1076,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6775,7 +6809,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="6">
-        <v>3727272</v>
+        <v>7454544</v>
       </c>
       <c r="AK34" s="6">
         <v>1</v>
@@ -6784,7 +6818,7 @@
         <v>1</v>
       </c>
       <c r="AM34" s="6">
-        <v>372727</v>
+        <v>909091</v>
       </c>
       <c r="AN34" s="7">
         <v>0</v>
@@ -20660,7 +20694,7 @@
       </c>
       <c r="I34">
         <f>UnitUpper!AJ34</f>
-        <v>3727272</v>
+        <v>7454544</v>
       </c>
       <c r="J34">
         <f>UnitUpper!AK34</f>
